--- a/data/Self_Port.xlsx
+++ b/data/Self_Port.xlsx
@@ -8,21 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\westl\PycharmProjects\pythonProject\venv_vf_new\port\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD770C0C-1575-4611-AE00-DDC66566D90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9605DD3-7BFF-4634-9FDE-C1B05A91CB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="936" windowWidth="12312" windowHeight="11304" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Universe" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -83,6 +96,10 @@
   </si>
   <si>
     <t>BAI US Equity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMZN US Equity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +108,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -129,9 +146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -434,8 +452,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="18.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -522,6 +543,62 @@
       </c>
       <c r="D6">
         <v>26.48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>63.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>271.89999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>215.23010000000011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2360000</v>
       </c>
     </row>
   </sheetData>
@@ -619,7 +696,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -711,6 +788,11 @@
         <v>15</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Self_Port.xlsx
+++ b/data/Self_Port.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\westl\PycharmProjects\pythonProject\venv_vf_new\port\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9605DD3-7BFF-4634-9FDE-C1B05A91CB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7754586B-01F2-4FA6-8AC8-57CD5883B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="936" windowWidth="12312" windowHeight="11304" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -101,6 +101,9 @@
   <si>
     <t>AMZN US Equity</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>442580 KS Equity</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.8984375" bestFit="1" customWidth="1"/>
@@ -589,16 +592,30 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
-        <v>46174</v>
+        <v>46184</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>2360000</v>
+        <v>2206333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>121159</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -793,6 +810,11 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Self_Port.xlsx
+++ b/data/Self_Port.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\westl\PycharmProjects\pythonProject\venv_vf_new\port\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7754586B-01F2-4FA6-8AC8-57CD5883B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A44453B-FF76-4CF7-AA79-A22BBF7BE884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -626,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.8984375" bestFit="1" customWidth="1"/>
@@ -703,6 +703,34 @@
       </c>
       <c r="D5">
         <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>71.349999999999994</v>
       </c>
     </row>
   </sheetData>
